--- a/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP100" headerRowCount="1">
-  <autoFilter ref="A1:EP100"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP101" headerRowCount="1">
+  <autoFilter ref="A1:EP101"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP100"/>
+  <dimension ref="A1:EP101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>3</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DE10" t="n">
         <v>0.33</v>
@@ -11697,7 +11697,7 @@
         <v>0.33</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -14046,7 +14046,7 @@
         <v>50</v>
       </c>
       <c r="DD28" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DE28" t="n">
         <v>0.83</v>
@@ -20581,7 +20581,7 @@
         <v>0.33</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DF42" t="n">
         <v>1</v>
@@ -21038,7 +21038,7 @@
         <v>75</v>
       </c>
       <c r="DD43" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DE43" t="n">
         <v>1.83</v>
@@ -23881,7 +23881,7 @@
         <v>2.2</v>
       </c>
       <c r="DE49" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DF49" t="n">
         <v>3</v>
@@ -26666,7 +26666,7 @@
         <v>84</v>
       </c>
       <c r="DD55" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DE55" t="n">
         <v>0.83</v>
@@ -31806,7 +31806,7 @@
         <v>75</v>
       </c>
       <c r="DD66" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DE66" t="n">
         <v>2.6</v>
@@ -32741,7 +32741,7 @@
         <v>1</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DF68" t="n">
         <v>1</v>
@@ -41685,7 +41685,7 @@
         <v>1.2</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DF87" t="n">
         <v>0.75</v>
@@ -42150,7 +42150,7 @@
         <v>50</v>
       </c>
       <c r="DD88" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="DE88" t="n">
         <v>1.17</v>
@@ -44607,43 +44607,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
         <v>45983.60416666666</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M94" t="n">
         <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -44655,98 +44655,98 @@
         <v>6</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V94" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X94" t="n">
         <v>10</v>
       </c>
       <c r="Y94" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z94" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Signal-Iduna-Park</t>
+          <t>WWK Arena</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>Strobelalle 50, Dortmund</t>
+          <t>Bürgermeister Ulrich-Straße 90, Augsburg</t>
         </is>
       </c>
       <c r="AC94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="AF94" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AG94" t="n">
-        <v>4.28</v>
+        <v>3.05</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AI94" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AK94" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL94" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="AM94" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AN94" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AO94" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AR94" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AS94" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="AT94" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AU94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW94" t="n">
         <v>0</v>
@@ -44755,22 +44755,22 @@
         <v>1</v>
       </c>
       <c r="AY94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB94" t="n">
-        <v>-1</v>
+        <v>50</v>
       </c>
       <c r="BC94" t="n">
         <v>0</v>
       </c>
       <c r="BD94" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="BE94" t="n">
         <v>0</v>
@@ -44785,7 +44785,7 @@
         <v>1</v>
       </c>
       <c r="BI94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ94" t="n">
         <v>2</v>
@@ -44794,16 +44794,16 @@
         <v>1</v>
       </c>
       <c r="BL94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BO94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP94" t="n">
         <v>1</v>
@@ -44812,13 +44812,13 @@
         <v>1</v>
       </c>
       <c r="BR94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU94" t="n">
         <v>1</v>
@@ -44827,31 +44827,31 @@
         <v>49</v>
       </c>
       <c r="BW94" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="BX94" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="BY94" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="BZ94" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="CA94" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="CB94" t="n">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="CC94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD94" t="n">
         <v>0</v>
       </c>
       <c r="CE94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF94" t="n">
         <v>0</v>
@@ -44875,10 +44875,10 @@
         <v>0</v>
       </c>
       <c r="CM94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO94" t="n">
         <v>0</v>
@@ -44890,73 +44890,73 @@
         <v>1</v>
       </c>
       <c r="CR94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY94" t="n">
         <v>9</v>
       </c>
-      <c r="CS94" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU94" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV94" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW94" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX94" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY94" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ94" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="DA94" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="DB94" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="DC94" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="DD94" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="DE94" t="n">
-        <v>1.17</v>
+        <v>0.33</v>
       </c>
       <c r="DF94" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="DG94" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="DH94" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="DI94" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="DJ94" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="DK94" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="DL94" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="DM94" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="DN94" t="n">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="DO94" t="n">
         <v>11</v>
@@ -44965,91 +44965,115 @@
         <v>1</v>
       </c>
       <c r="DQ94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW94" t="n">
-        <v>2.85</v>
+        <v>0.13</v>
       </c>
       <c r="DX94" t="n">
-        <v>4.06</v>
+        <v>1.63</v>
       </c>
       <c r="DY94" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="DZ94" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="EA94" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EB94" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EC94" t="inlineStr"/>
-      <c r="ED94" t="inlineStr"/>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="ED94" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="EE94" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="EF94" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EG94" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EH94" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="EI94" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EJ94" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK94" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="EL94" t="inlineStr"/>
-      <c r="EM94" t="inlineStr"/>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EL94" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EM94" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
       <c r="EN94" t="inlineStr"/>
-      <c r="EO94" t="inlineStr"/>
-      <c r="EP94" t="inlineStr"/>
+      <c r="EO94" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EP94" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -45067,170 +45091,170 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
         <v>45983.60416666666</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J95" t="n">
+        <v>3</v>
+      </c>
+      <c r="K95" t="n">
+        <v>5</v>
+      </c>
+      <c r="L95" t="n">
+        <v>8</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>8</v>
+      </c>
+      <c r="R95" t="n">
+        <v>2</v>
+      </c>
+      <c r="S95" t="n">
+        <v>14</v>
+      </c>
+      <c r="T95" t="n">
+        <v>6</v>
+      </c>
+      <c r="U95" t="n">
+        <v>22</v>
+      </c>
+      <c r="V95" t="n">
+        <v>8</v>
+      </c>
+      <c r="W95" t="n">
+        <v>9</v>
+      </c>
+      <c r="X95" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Allianz Arena</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Werner-Heisenberg-Allee 25, München</t>
+        </is>
+      </c>
+      <c r="AC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX95" t="n">
         <v>4</v>
       </c>
-      <c r="K95" t="n">
-        <v>3</v>
-      </c>
-      <c r="L95" t="n">
-        <v>7</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" t="n">
-        <v>3</v>
-      </c>
-      <c r="O95" t="n">
-        <v>1</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>6</v>
-      </c>
-      <c r="R95" t="n">
-        <v>6</v>
-      </c>
-      <c r="S95" t="n">
-        <v>7</v>
-      </c>
-      <c r="T95" t="n">
-        <v>9</v>
-      </c>
-      <c r="U95" t="n">
-        <v>13</v>
-      </c>
-      <c r="V95" t="n">
-        <v>15</v>
-      </c>
-      <c r="W95" t="n">
-        <v>13</v>
-      </c>
-      <c r="X95" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>WWK Arena</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>Bürgermeister Ulrich-Straße 90, Augsburg</t>
-        </is>
-      </c>
-      <c r="AC95" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD95" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE95" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AF95" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG95" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH95" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI95" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AJ95" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK95" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL95" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AM95" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN95" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AO95" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AP95" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AQ95" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR95" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS95" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AT95" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW95" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX95" t="n">
-        <v>1</v>
-      </c>
       <c r="AY95" t="n">
         <v>0</v>
       </c>
       <c r="AZ95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB95" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BC95" t="n">
         <v>0</v>
       </c>
       <c r="BD95" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="BE95" t="n">
         <v>0</v>
@@ -45245,13 +45269,13 @@
         <v>1</v>
       </c>
       <c r="BI95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL95" t="n">
         <v>1</v>
@@ -45260,49 +45284,49 @@
         <v>5</v>
       </c>
       <c r="BN95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BO95" t="n">
         <v>1</v>
       </c>
       <c r="BP95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU95" t="n">
         <v>1</v>
       </c>
       <c r="BV95" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="BW95" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="BX95" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="BY95" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="BZ95" t="n">
-        <v>1.59</v>
+        <v>2.37</v>
       </c>
       <c r="CA95" t="n">
-        <v>1.64</v>
+        <v>0.84</v>
       </c>
       <c r="CB95" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CC95" t="n">
         <v>0</v>
@@ -45335,10 +45359,10 @@
         <v>0</v>
       </c>
       <c r="CM95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO95" t="n">
         <v>0</v>
@@ -45350,25 +45374,25 @@
         <v>1</v>
       </c>
       <c r="CR95" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CS95" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="CT95" t="n">
         <v>1</v>
       </c>
       <c r="CU95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CV95" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CW95" t="n">
         <v>1</v>
       </c>
       <c r="CX95" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY95" t="n">
         <v>9</v>
@@ -45377,7 +45401,7 @@
         <v>70</v>
       </c>
       <c r="DA95" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="DB95" t="n">
         <v>40</v>
@@ -45386,37 +45410,37 @@
         <v>80</v>
       </c>
       <c r="DD95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
       <c r="DF95" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="DG95" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DH95" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="DI95" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="DJ95" t="n">
         <v>30</v>
       </c>
       <c r="DK95" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DL95" t="n">
-        <v>1.35</v>
+        <v>2.37</v>
       </c>
       <c r="DM95" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="DN95" t="n">
-        <v>2.56</v>
+        <v>3.61</v>
       </c>
       <c r="DO95" t="n">
         <v>11</v>
@@ -45425,115 +45449,107 @@
         <v>1</v>
       </c>
       <c r="DQ95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW95" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="DX95" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DY95" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="DZ95" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EA95" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EB95" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EC95" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="ED95" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EE95" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="EF95" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="EG95" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="EH95" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EI95" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EJ95" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EK95" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EL95" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EM95" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EN95" t="inlineStr"/>
-      <c r="EO95" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="EP95" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
+      <c r="EO95" t="inlineStr"/>
+      <c r="EP95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -45551,40 +45567,40 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
         <v>45983.60416666666</v>
       </c>
       <c r="G96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -45593,128 +45609,128 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S96" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U96" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V96" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W96" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="X96" t="n">
         <v>7</v>
       </c>
       <c r="Y96" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="Z96" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Allianz Arena</t>
+          <t>VOLKSWAGEN ARENA</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>Werner-Heisenberg-Allee 25, München</t>
+          <t>In den Allerwiesen 1, Wolfsburg</t>
         </is>
       </c>
       <c r="AC96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.19</v>
+        <v>3.58</v>
       </c>
       <c r="AF96" t="n">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="AG96" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI96" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AJ96" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AK96" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL96" t="n">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="AM96" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT96" t="n">
         <v>1.58</v>
       </c>
-      <c r="AN96" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AP96" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR96" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AS96" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT96" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AU96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AV96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY96" t="n">
         <v>0</v>
       </c>
       <c r="AZ96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB96" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC96" t="n">
         <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="BE96" t="n">
         <v>0</v>
@@ -45729,25 +45745,25 @@
         <v>1</v>
       </c>
       <c r="BI96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK96" t="n">
         <v>4</v>
       </c>
-      <c r="BK96" t="n">
-        <v>2</v>
-      </c>
       <c r="BL96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP96" t="n">
         <v>0</v>
@@ -45756,37 +45772,37 @@
         <v>0</v>
       </c>
       <c r="BR96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU96" t="n">
         <v>1</v>
       </c>
       <c r="BV96" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="BW96" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="BX96" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="BY96" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="BZ96" t="n">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="CA96" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="CB96" t="n">
-        <v>3.21</v>
+        <v>3.52</v>
       </c>
       <c r="CC96" t="n">
         <v>0</v>
@@ -45816,13 +45832,13 @@
         <v>0</v>
       </c>
       <c r="CL96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM96" t="n">
         <v>0</v>
       </c>
       <c r="CN96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO96" t="n">
         <v>0</v>
@@ -45834,10 +45850,10 @@
         <v>1</v>
       </c>
       <c r="CR96" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CS96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT96" t="n">
         <v>1</v>
@@ -45846,7 +45862,7 @@
         <v>7</v>
       </c>
       <c r="CV96" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CW96" t="n">
         <v>1</v>
@@ -45855,52 +45871,52 @@
         <v>5</v>
       </c>
       <c r="CY96" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CZ96" t="n">
+        <v>80</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB96" t="n">
         <v>70</v>
       </c>
-      <c r="DA96" t="n">
-        <v>80</v>
-      </c>
-      <c r="DB96" t="n">
-        <v>40</v>
-      </c>
       <c r="DC96" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="DD96" t="n">
-        <v>3</v>
+        <v>0.33</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.83</v>
+        <v>2</v>
       </c>
       <c r="DF96" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="DG96" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH96" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="DI96" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="DJ96" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DK96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL96" t="n">
-        <v>2.37</v>
+        <v>1.58</v>
       </c>
       <c r="DM96" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DN96" t="n">
-        <v>3.61</v>
+        <v>2.81</v>
       </c>
       <c r="DO96" t="n">
         <v>11</v>
@@ -45918,95 +45934,71 @@
         <v>1</v>
       </c>
       <c r="DT96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV96" t="b">
         <v>1</v>
       </c>
       <c r="DW96" t="n">
-        <v>0.02</v>
+        <v>1.83</v>
       </c>
       <c r="DX96" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="DY96" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="DZ96" t="inlineStr">
         <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="EA96" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EB96" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EC96" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="ED96" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="EA96" t="inlineStr"/>
+      <c r="EB96" t="inlineStr"/>
+      <c r="EC96" t="inlineStr"/>
+      <c r="ED96" t="inlineStr"/>
       <c r="EE96" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EF96" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="EG96" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="EH96" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EI96" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EJ96" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EK96" t="inlineStr">
         <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EL96" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EM96" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr"/>
+      <c r="EM96" t="inlineStr"/>
       <c r="EN96" t="inlineStr"/>
       <c r="EO96" t="inlineStr"/>
       <c r="EP96" t="inlineStr"/>
@@ -46027,170 +46019,170 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
         <v>45983.60416666666</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H97" t="n">
         <v>3</v>
       </c>
       <c r="I97" t="n">
+        <v>6</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
         <v>4</v>
       </c>
-      <c r="J97" t="n">
-        <v>9</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
-      </c>
       <c r="L97" t="n">
+        <v>6</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>6</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6</v>
+      </c>
+      <c r="S97" t="n">
+        <v>8</v>
+      </c>
+      <c r="T97" t="n">
         <v>10</v>
       </c>
-      <c r="M97" t="n">
-        <v>2</v>
-      </c>
-      <c r="N97" t="n">
-        <v>1</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>10</v>
-      </c>
-      <c r="R97" t="n">
-        <v>3</v>
-      </c>
-      <c r="S97" t="n">
-        <v>11</v>
-      </c>
-      <c r="T97" t="n">
-        <v>4</v>
-      </c>
       <c r="U97" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V97" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
       </c>
       <c r="X97" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y97" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Z97" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN ARENA</t>
+          <t>Signal-Iduna-Park</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>In den Allerwiesen 1, Wolfsburg</t>
+          <t>Strobelalle 50, Dortmund</t>
         </is>
       </c>
       <c r="AC97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD97" t="n">
         <v>1</v>
       </c>
       <c r="AE97" t="n">
-        <v>3.58</v>
+        <v>1.79</v>
       </c>
       <c r="AF97" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AG97" t="n">
-        <v>2</v>
+        <v>4.28</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AI97" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AJ97" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AK97" t="n">
         <v>1.53</v>
       </c>
       <c r="AL97" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AM97" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AN97" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AO97" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AP97" t="n">
         <v>2.05</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AR97" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AS97" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AT97" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AU97" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ97" t="n">
         <v>4</v>
       </c>
-      <c r="AV97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW97" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY97" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ97" t="n">
-        <v>1</v>
-      </c>
       <c r="BA97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB97" t="n">
-        <v>40</v>
+        <v>-1</v>
       </c>
       <c r="BC97" t="n">
         <v>0</v>
       </c>
       <c r="BD97" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="BE97" t="n">
         <v>0</v>
@@ -46205,37 +46197,37 @@
         <v>1</v>
       </c>
       <c r="BI97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BJ97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM97" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BN97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT97" t="n">
         <v>1</v>
@@ -46244,34 +46236,34 @@
         <v>1</v>
       </c>
       <c r="BV97" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="BW97" t="n">
         <v>52</v>
       </c>
       <c r="BX97" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="BY97" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="BZ97" t="n">
-        <v>2.49</v>
+        <v>1.66</v>
       </c>
       <c r="CA97" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="CB97" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="CC97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD97" t="n">
         <v>0</v>
       </c>
       <c r="CE97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF97" t="n">
         <v>0</v>
@@ -46292,13 +46284,13 @@
         <v>0</v>
       </c>
       <c r="CL97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM97" t="n">
         <v>0</v>
       </c>
       <c r="CN97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO97" t="n">
         <v>0</v>
@@ -46310,16 +46302,16 @@
         <v>1</v>
       </c>
       <c r="CR97" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CS97" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CT97" t="n">
         <v>1</v>
       </c>
       <c r="CU97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CV97" t="n">
         <v>12</v>
@@ -46328,55 +46320,55 @@
         <v>1</v>
       </c>
       <c r="CX97" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY97" t="n">
         <v>5</v>
       </c>
-      <c r="CY97" t="n">
-        <v>12</v>
-      </c>
       <c r="CZ97" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="DA97" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="DB97" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="DC97" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DD97" t="n">
-        <v>0.33</v>
+        <v>2.2</v>
       </c>
       <c r="DE97" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="DF97" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="DG97" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="DH97" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="DI97" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DJ97" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="DK97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="DL97" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="DM97" t="n">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="DN97" t="n">
-        <v>2.81</v>
+        <v>3.75</v>
       </c>
       <c r="DO97" t="n">
         <v>11</v>
@@ -46394,23 +46386,23 @@
         <v>1</v>
       </c>
       <c r="DT97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV97" t="b">
         <v>1</v>
       </c>
       <c r="DW97" t="n">
-        <v>1.83</v>
+        <v>2.85</v>
       </c>
       <c r="DX97" t="n">
-        <v>2.88</v>
+        <v>4.06</v>
       </c>
       <c r="DY97" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ97" t="inlineStr">
@@ -46418,43 +46410,51 @@
           <t>15%</t>
         </is>
       </c>
-      <c r="EA97" t="inlineStr"/>
-      <c r="EB97" t="inlineStr"/>
+      <c r="EA97" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
       <c r="EC97" t="inlineStr"/>
       <c r="ED97" t="inlineStr"/>
       <c r="EE97" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="EF97" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EG97" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EH97" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EI97" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EJ97" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EK97" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EL97" t="inlineStr"/>
@@ -47827,6 +47827,474 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Germany_Bundesliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>12</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Borussia M'gladbach</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>45989.8125</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>5</v>
+      </c>
+      <c r="K101" t="n">
+        <v>6</v>
+      </c>
+      <c r="L101" t="n">
+        <v>11</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>4</v>
+      </c>
+      <c r="S101" t="n">
+        <v>7</v>
+      </c>
+      <c r="T101" t="n">
+        <v>16</v>
+      </c>
+      <c r="U101" t="n">
+        <v>7</v>
+      </c>
+      <c r="V101" t="n">
+        <v>20</v>
+      </c>
+      <c r="W101" t="n">
+        <v>9</v>
+      </c>
+      <c r="X101" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Stadion im BORUSSIA-PARK</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Hennes-Weisweiler-Allee 1, Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>33</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>71</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>137</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>33</v>
+      </c>
+      <c r="DL101" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM101" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DN101" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DO101" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW101" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="DX101" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="ED101" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EE101" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EF101" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EG101" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EJ101" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK101" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EL101" t="inlineStr"/>
+      <c r="EM101" t="inlineStr"/>
+      <c r="EN101" t="inlineStr"/>
+      <c r="EO101" t="inlineStr"/>
+      <c r="EP101" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
@@ -53102,13 +53102,13 @@
         <v>13</v>
       </c>
       <c r="T112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U112" t="n">
         <v>16</v>
       </c>
       <c r="V112" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W112" t="n">
         <v>11</v>
@@ -53117,10 +53117,10 @@
         <v>10</v>
       </c>
       <c r="Y112" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Z112" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
@@ -53283,10 +53283,10 @@
         <v>1.49</v>
       </c>
       <c r="CA112" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="CB112" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="CC112" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
@@ -59226,7 +59226,7 @@
         <v>11</v>
       </c>
       <c r="X125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y125" t="n">
         <v>57</v>
@@ -59455,7 +59455,7 @@
         <v>1</v>
       </c>
       <c r="CU125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CV125" t="n">
         <v>11</v>
@@ -60165,19 +60165,19 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
         <v>12</v>
       </c>
       <c r="S127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T127" t="n">
         <v>12</v>
       </c>
       <c r="U127" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V127" t="n">
         <v>24</v>
@@ -60189,10 +60189,10 @@
         <v>6</v>
       </c>
       <c r="Y127" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z127" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr"/>
@@ -60344,13 +60344,13 @@
         <v>125</v>
       </c>
       <c r="BZ127" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="CA127" t="n">
         <v>2.84</v>
       </c>
       <c r="CB127" t="n">
-        <v>3.82</v>
+        <v>4.01</v>
       </c>
       <c r="CC127" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
@@ -31955,12 +31955,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
@@ -31970,155 +31970,155 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
+        <v>6</v>
+      </c>
+      <c r="I67" t="n">
+        <v>6</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" t="n">
         <v>3</v>
       </c>
-      <c r="I67" t="n">
+      <c r="L67" t="n">
+        <v>5</v>
+      </c>
+      <c r="M67" t="n">
         <v>3</v>
       </c>
-      <c r="J67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" t="n">
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R67" t="n">
         <v>8</v>
       </c>
-      <c r="L67" t="n">
+      <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
+        <v>7</v>
+      </c>
+      <c r="U67" t="n">
+        <v>15</v>
+      </c>
+      <c r="V67" t="n">
+        <v>15</v>
+      </c>
+      <c r="W67" t="n">
         <v>9</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
+      <c r="X67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>WWK Arena</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Bürgermeister Ulrich-Straße 90, Augsburg</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
         <v>3</v>
       </c>
-      <c r="O67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>11</v>
-      </c>
-      <c r="S67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T67" t="n">
-        <v>16</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="n">
-        <v>27</v>
-      </c>
-      <c r="W67" t="n">
+      <c r="AD67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU67" t="n">
         <v>6</v>
       </c>
-      <c r="X67" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>83</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>Stadion im BORUSSIA-PARK</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>Hennes-Weisweiler-Allee 1, Mönchengladbach</t>
-        </is>
-      </c>
-      <c r="AC67" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>3</v>
-      </c>
       <c r="AV67" t="n">
         <v>0</v>
       </c>
       <c r="AW67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX67" t="n">
         <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB67" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BC67" t="n">
         <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="BE67" t="n">
         <v>0</v>
@@ -32133,136 +32133,136 @@
         <v>1</v>
       </c>
       <c r="BI67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN67" t="n">
         <v>4</v>
       </c>
-      <c r="BK67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL67" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM67" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN67" t="n">
-        <v>5</v>
-      </c>
       <c r="BO67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR67" t="n">
         <v>1</v>
       </c>
       <c r="BS67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>146</v>
+      </c>
+      <c r="BY67" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ67" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA67" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CB67" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR67" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS67" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU67" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV67" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW67" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX67" t="n">
         <v>3</v>
       </c>
-      <c r="BT67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV67" t="n">
-        <v>16</v>
-      </c>
-      <c r="BW67" t="n">
-        <v>129</v>
-      </c>
-      <c r="BX67" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY67" t="n">
-        <v>176</v>
-      </c>
-      <c r="BZ67" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="CA67" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="CB67" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="CC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN67" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP67" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR67" t="n">
+      <c r="CY67" t="n">
         <v>13</v>
       </c>
-      <c r="CS67" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU67" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV67" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW67" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX67" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY67" t="n">
-        <v>1</v>
-      </c>
       <c r="CZ67" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DA67" t="n">
         <v>75</v>
@@ -32271,40 +32271,40 @@
         <v>59</v>
       </c>
       <c r="DC67" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="DE67" t="n">
-        <v>2.71</v>
+        <v>1.38</v>
       </c>
       <c r="DF67" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DG67" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="DH67" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="DI67" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="DJ67" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DK67" t="n">
         <v>25</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DM67" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="DN67" t="n">
-        <v>3.58</v>
+        <v>2.99</v>
       </c>
       <c r="DO67" t="n">
         <v>15</v>
@@ -32319,41 +32319,41 @@
         <v>1</v>
       </c>
       <c r="DS67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV67" t="b">
         <v>0</v>
       </c>
       <c r="DW67" t="n">
-        <v>9.91</v>
+        <v>9.6</v>
       </c>
       <c r="DX67" t="n">
-        <v>9.65</v>
+        <v>9.82</v>
       </c>
       <c r="DY67" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ67" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA67" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EB67" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EC67" t="inlineStr">
@@ -32368,33 +32368,37 @@
       </c>
       <c r="EE67" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EF67" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EG67" t="inlineStr">
         <is>
-          <t>10.35</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EH67" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EI67" t="inlineStr"/>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EI67" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
       <c r="EJ67" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EK67" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="EL67" t="inlineStr"/>
@@ -32419,170 +32423,170 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
         <v>45955.5625</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H68" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K68" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>12</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>7</v>
+      </c>
+      <c r="R68" t="n">
         <v>3</v>
       </c>
-      <c r="L68" t="n">
-        <v>5</v>
-      </c>
-      <c r="M68" t="n">
-        <v>3</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>2</v>
-      </c>
-      <c r="R68" t="n">
-        <v>8</v>
-      </c>
       <c r="S68" t="n">
+        <v>7</v>
+      </c>
+      <c r="T68" t="n">
+        <v>9</v>
+      </c>
+      <c r="U68" t="n">
+        <v>14</v>
+      </c>
+      <c r="V68" t="n">
+        <v>12</v>
+      </c>
+      <c r="W68" t="n">
+        <v>14</v>
+      </c>
+      <c r="X68" t="n">
         <v>13</v>
       </c>
-      <c r="T68" t="n">
-        <v>7</v>
-      </c>
-      <c r="U68" t="n">
-        <v>15</v>
-      </c>
-      <c r="V68" t="n">
-        <v>15</v>
-      </c>
-      <c r="W68" t="n">
-        <v>9</v>
-      </c>
-      <c r="X68" t="n">
-        <v>10</v>
-      </c>
       <c r="Y68" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Z68" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>WWK Arena</t>
+          <t>WIRSOL Rhein-Neckar-Arena</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Bürgermeister Ulrich-Straße 90, Augsburg</t>
+          <t>Dietmar-Hopp-Straße 1, Sinsheim</t>
         </is>
       </c>
       <c r="AC68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD68" t="n">
         <v>1</v>
       </c>
       <c r="AE68" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="AF68" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AG68" t="n">
-        <v>2</v>
+        <v>5.25</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AJ68" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AL68" t="n">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="AM68" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AN68" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AO68" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AR68" t="n">
         <v>2.1</v>
       </c>
       <c r="AS68" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AT68" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AU68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ68" t="n">
         <v>2</v>
       </c>
       <c r="BA68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB68" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="BC68" t="n">
         <v>0</v>
       </c>
       <c r="BD68" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="BE68" t="n">
         <v>0</v>
@@ -32597,178 +32601,178 @@
         <v>1</v>
       </c>
       <c r="BI68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ68" t="n">
         <v>0</v>
       </c>
       <c r="BK68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL68" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM68" t="n">
         <v>3</v>
       </c>
-      <c r="BM68" t="n">
-        <v>1</v>
-      </c>
       <c r="BN68" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>96</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB68" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR68" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS68" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU68" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV68" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX68" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY68" t="n">
         <v>4</v>
       </c>
-      <c r="BO68" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ68" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR68" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS68" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT68" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU68" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV68" t="n">
-        <v>43</v>
-      </c>
-      <c r="BW68" t="n">
+      <c r="CZ68" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA68" t="n">
+        <v>67</v>
+      </c>
+      <c r="DB68" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC68" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD68" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE68" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH68" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DI68" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DJ68" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK68" t="n">
         <v>33</v>
       </c>
-      <c r="BX68" t="n">
-        <v>146</v>
-      </c>
-      <c r="BY68" t="n">
-        <v>78</v>
-      </c>
-      <c r="BZ68" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CA68" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CB68" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI68" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ68" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL68" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ68" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR68" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS68" t="n">
-        <v>9</v>
-      </c>
-      <c r="CT68" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU68" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV68" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW68" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX68" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY68" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ68" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA68" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB68" t="n">
-        <v>59</v>
-      </c>
-      <c r="DC68" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD68" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DE68" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DF68" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG68" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DH68" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI68" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="DJ68" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK68" t="n">
-        <v>25</v>
-      </c>
       <c r="DL68" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="DM68" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="DN68" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="DO68" t="n">
         <v>15</v>
@@ -32786,68 +32790,68 @@
         <v>1</v>
       </c>
       <c r="DT68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW68" t="n">
-        <v>9.6</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DX68" t="n">
-        <v>9.82</v>
+        <v>10.6</v>
       </c>
       <c r="DY68" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ68" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA68" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EB68" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EC68" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="ED68" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EE68" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="EF68" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EG68" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EH68" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EI68" t="inlineStr">
@@ -32857,12 +32861,12 @@
       </c>
       <c r="EJ68" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EK68" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EL68" t="inlineStr"/>
@@ -32887,31 +32891,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
         <v>45955.5625</v>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>12</v>
@@ -32920,7 +32924,7 @@
         <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -32929,122 +32933,122 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="T69" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U69" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="V69" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="W69" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X69" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Y69" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z69" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>WIRSOL Rhein-Neckar-Arena</t>
+          <t>Volksparkstadion</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Dietmar-Hopp-Straße 1, Sinsheim</t>
+          <t>Sylvester Allee 7, Hamburg</t>
         </is>
       </c>
       <c r="AC69" t="n">
         <v>1</v>
       </c>
       <c r="AD69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="AF69" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="AG69" t="n">
-        <v>5.25</v>
+        <v>3.13</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AL69" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AM69" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AN69" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AO69" t="n">
         <v>2.63</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AR69" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AS69" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AU69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
@@ -33068,61 +33072,61 @@
         <v>3</v>
       </c>
       <c r="BJ69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK69" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM69" t="n">
         <v>4</v>
       </c>
-      <c r="BL69" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM69" t="n">
+      <c r="BN69" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR69" t="n">
         <v>3</v>
       </c>
-      <c r="BN69" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO69" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP69" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR69" t="n">
-        <v>1</v>
-      </c>
       <c r="BS69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
       </c>
       <c r="BV69" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="BW69" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="BX69" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="BY69" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="BZ69" t="n">
-        <v>1.74</v>
+        <v>2.67</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.26</v>
+        <v>0.68</v>
       </c>
       <c r="CB69" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="CC69" t="n">
         <v>0</v>
@@ -33155,7 +33159,7 @@
         <v>0</v>
       </c>
       <c r="CM69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN69" t="n">
         <v>0</v>
@@ -33170,19 +33174,19 @@
         <v>1</v>
       </c>
       <c r="CR69" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CS69" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CT69" t="n">
         <v>1</v>
       </c>
       <c r="CU69" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="CV69" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CW69" t="n">
         <v>1</v>
@@ -33191,52 +33195,52 @@
         <v>6</v>
       </c>
       <c r="CY69" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="CZ69" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DA69" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB69" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC69" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD69" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE69" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DF69" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH69" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DI69" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>33</v>
+      </c>
+      <c r="DK69" t="n">
         <v>17</v>
       </c>
-      <c r="DC69" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD69" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DE69" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH69" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DI69" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="DJ69" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK69" t="n">
-        <v>33</v>
-      </c>
       <c r="DL69" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="DO69" t="n">
         <v>15</v>
@@ -33245,13 +33249,13 @@
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT69" t="b">
         <v>0</v>
@@ -33260,81 +33264,89 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW69" t="n">
-        <v>9.880000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="DX69" t="n">
-        <v>10.6</v>
+        <v>7.44</v>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EB69" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EC69" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="ED69" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EE69" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EF69" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="EG69" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EH69" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EI69" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EJ69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EK69" t="inlineStr">
         <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EL69" t="inlineStr"/>
-      <c r="EM69" t="inlineStr"/>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EL69" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EM69" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
       <c r="EN69" t="inlineStr"/>
       <c r="EO69" t="inlineStr"/>
       <c r="EP69" t="inlineStr"/>
@@ -33355,170 +33367,170 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45955.5625</v>
+        <v>45955.57291666666</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>8</v>
+      </c>
+      <c r="L70" t="n">
+        <v>9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
         <v>11</v>
       </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" t="n">
-        <v>12</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" t="n">
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>16</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>27</v>
+      </c>
+      <c r="W70" t="n">
+        <v>6</v>
+      </c>
+      <c r="X70" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Stadion im BORUSSIA-PARK</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Hennes-Weisweiler-Allee 1, Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="AC70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS70" t="n">
         <v>5</v>
       </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>6</v>
-      </c>
-      <c r="R70" t="n">
-        <v>2</v>
-      </c>
-      <c r="S70" t="n">
-        <v>21</v>
-      </c>
-      <c r="T70" t="n">
-        <v>4</v>
-      </c>
-      <c r="U70" t="n">
-        <v>27</v>
-      </c>
-      <c r="V70" t="n">
-        <v>6</v>
-      </c>
-      <c r="W70" t="n">
-        <v>8</v>
-      </c>
-      <c r="X70" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>Volksparkstadion</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>Sylvester Allee 7, Hamburg</t>
-        </is>
-      </c>
-      <c r="AC70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AT70" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV70" t="n">
         <v>0</v>
       </c>
       <c r="AW70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX70" t="n">
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB70" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -33533,178 +33545,178 @@
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BL70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BM70" t="n">
         <v>4</v>
       </c>
       <c r="BN70" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>129</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>176</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU70" t="n">
         <v>8</v>
       </c>
-      <c r="BO70" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP70" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR70" t="n">
+      <c r="CV70" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>59</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG70" t="n">
         <v>3</v>
       </c>
-      <c r="BS70" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT70" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU70" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV70" t="n">
-        <v>78</v>
-      </c>
-      <c r="BW70" t="n">
-        <v>20</v>
-      </c>
-      <c r="BX70" t="n">
-        <v>112</v>
-      </c>
-      <c r="BY70" t="n">
-        <v>78</v>
-      </c>
-      <c r="BZ70" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CA70" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="CB70" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="CC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM70" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>23</v>
-      </c>
-      <c r="CS70" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU70" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV70" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX70" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY70" t="n">
-        <v>19</v>
-      </c>
-      <c r="CZ70" t="n">
-        <v>67</v>
-      </c>
-      <c r="DA70" t="n">
-        <v>84</v>
-      </c>
-      <c r="DB70" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC70" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD70" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DE70" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DF70" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG70" t="n">
-        <v>1</v>
-      </c>
       <c r="DH70" t="n">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
       <c r="DI70" t="n">
-        <v>0.71</v>
+        <v>3</v>
       </c>
       <c r="DJ70" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="DK70" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="DO70" t="n">
         <v>15</v>
@@ -33713,10 +33725,10 @@
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -33731,14 +33743,14 @@
         <v>0</v>
       </c>
       <c r="DW70" t="n">
-        <v>9.19</v>
+        <v>9.91</v>
       </c>
       <c r="DX70" t="n">
-        <v>7.44</v>
+        <v>9.65</v>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="DZ70" t="inlineStr">
@@ -33748,12 +33760,12 @@
       </c>
       <c r="EA70" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EB70" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EC70" t="inlineStr">
@@ -33768,49 +33780,37 @@
       </c>
       <c r="EE70" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EF70" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="EG70" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>10.35</t>
         </is>
       </c>
       <c r="EH70" t="inlineStr">
         <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="EI70" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EI70" t="inlineStr"/>
       <c r="EJ70" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK70" t="inlineStr">
         <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EL70" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EM70" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EL70" t="inlineStr"/>
+      <c r="EM70" t="inlineStr"/>
       <c r="EN70" t="inlineStr"/>
       <c r="EO70" t="inlineStr"/>
       <c r="EP70" t="inlineStr"/>
@@ -37165,7 +37165,7 @@
         <v>10</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
         <v>2</v>
@@ -37209,7 +37209,7 @@
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>2</v>
@@ -37323,7 +37323,7 @@
         <v>6</v>
       </c>
       <c r="BO78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP78" t="n">
         <v>0</v>
@@ -37335,7 +37335,7 @@
         <v>2</v>
       </c>
       <c r="BS78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT78" t="n">
         <v>2</v>
@@ -42321,7 +42321,7 @@
         <v>12</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N89" t="n">
         <v>2</v>
@@ -42373,7 +42373,7 @@
         </is>
       </c>
       <c r="AC89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD89" t="n">
         <v>2</v>
@@ -42493,7 +42493,7 @@
         <v>0</v>
       </c>
       <c r="BQ89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR89" t="n">
         <v>2</v>
@@ -42502,7 +42502,7 @@
         <v>0</v>
       </c>
       <c r="BT89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU89" t="n">
         <v>1</v>
@@ -42800,7 +42800,7 @@
         <v>2</v>
       </c>
       <c r="N90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -42852,7 +42852,7 @@
         <v>2</v>
       </c>
       <c r="AD90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE90" t="n">
         <v>1.54</v>
@@ -42966,7 +42966,7 @@
         <v>0</v>
       </c>
       <c r="BP90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ90" t="n">
         <v>2</v>
@@ -42975,7 +42975,7 @@
         <v>2</v>
       </c>
       <c r="BS90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90" t="n">
         <v>4</v>
@@ -60287,28 +60287,28 @@
         <v>-1</v>
       </c>
       <c r="BG127" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH127" t="n">
         <v>1</v>
       </c>
       <c r="BI127" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BJ127" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK127" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL127" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BM127" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN127" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BO127" t="n">
         <v>1</v>
@@ -60383,10 +60383,10 @@
         <v>0</v>
       </c>
       <c r="CM127" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN127" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO127" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
@@ -75754,13 +75754,13 @@
         <v>8</v>
       </c>
       <c r="T160" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U160" t="n">
         <v>13</v>
       </c>
       <c r="V160" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W160" t="n">
         <v>11</v>
@@ -75935,10 +75935,10 @@
         <v>1.41</v>
       </c>
       <c r="CA160" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="CB160" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="CC160" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
@@ -81769,10 +81769,10 @@
         <v>14</v>
       </c>
       <c r="Y179" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z179" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA179" t="inlineStr">
         <is>

--- a/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2025-2026.xlsx
@@ -103188,7 +103188,7 @@
         <v>0</v>
       </c>
       <c r="BF226" t="n">
-        <v>-1</v>
+        <v>22012</v>
       </c>
       <c r="BG226" t="n">
         <v>2</v>
